--- a/PK/Exp2025-FashionMNIST-Dir0.5/cnn-dir0.5baseline_300.xlsx
+++ b/PK/Exp2025-FashionMNIST-Dir0.5/cnn-dir0.5baseline_300.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -519,7 +519,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>nonIID(0.5)</t>
+          <t>nonIID(timefirst)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -528,64 +528,64 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="D3" t="n">
-        <v>5.28</v>
+        <v>10.28</v>
       </c>
       <c r="E3" t="n">
-        <v>80</v>
+        <v>124</v>
       </c>
       <c r="F3" t="n">
-        <v>14.31</v>
+        <v>22.51</v>
       </c>
       <c r="G3" t="n">
-        <v>158</v>
+        <v>248</v>
       </c>
       <c r="H3" t="n">
-        <v>28.74</v>
+        <v>44.91</v>
       </c>
       <c r="I3" t="n">
-        <v>54.95</v>
+        <v>54.31</v>
       </c>
       <c r="J3" t="n">
-        <v>87.76000000000001</v>
+        <v>85.75</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>nonIID(0.5)</t>
+          <t>nonIID(plus)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>FedDocs</t>
+          <t>PyramidFL</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D4" t="n">
-        <v>7.27</v>
+        <v>7.15</v>
       </c>
       <c r="E4" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="F4" t="n">
-        <v>16.54</v>
+        <v>17.49</v>
       </c>
       <c r="G4" t="n">
-        <v>185</v>
+        <v>233</v>
       </c>
       <c r="H4" t="n">
-        <v>33.92</v>
+        <v>43.85</v>
       </c>
       <c r="I4" t="n">
-        <v>54.97</v>
+        <v>56.58</v>
       </c>
       <c r="J4" t="n">
-        <v>86.89</v>
+        <v>86.40000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -596,32 +596,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>FedLC</t>
+          <t>FedDocs</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D5" t="n">
-        <v>7.8</v>
+        <v>7.27</v>
       </c>
       <c r="E5" t="n">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="F5" t="n">
-        <v>19.33</v>
+        <v>16.54</v>
       </c>
       <c r="G5" t="n">
-        <v>225</v>
+        <v>185</v>
       </c>
       <c r="H5" t="n">
-        <v>41.17</v>
+        <v>33.92</v>
       </c>
       <c r="I5" t="n">
-        <v>54.89</v>
+        <v>54.97</v>
       </c>
       <c r="J5" t="n">
-        <v>86.52</v>
+        <v>86.89</v>
       </c>
     </row>
     <row r="6">
@@ -632,31 +632,67 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>FedLC</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>43</v>
+      </c>
+      <c r="D6" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="E6" t="n">
+        <v>106</v>
+      </c>
+      <c r="F6" t="n">
+        <v>19.33</v>
+      </c>
+      <c r="G6" t="n">
+        <v>225</v>
+      </c>
+      <c r="H6" t="n">
+        <v>41.17</v>
+      </c>
+      <c r="I6" t="n">
+        <v>54.89</v>
+      </c>
+      <c r="J6" t="n">
+        <v>86.52</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>nonIID(0.5)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>FedAvg</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="C7" t="n">
         <v>62</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D7" t="n">
         <v>11.29</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E7" t="n">
         <v>135</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F7" t="n">
         <v>24.54</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G7" t="n">
         <v>290</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H7" t="n">
         <v>53.24</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I7" t="n">
         <v>55.05</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J7" t="n">
         <v>85.09</v>
       </c>
     </row>

--- a/PK/Exp2025-FashionMNIST-Dir0.5/cnn-dir0.5baseline_300.xlsx
+++ b/PK/Exp2025-FashionMNIST-Dir0.5/cnn-dir0.5baseline_300.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,22 +495,22 @@
         <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>2.79</v>
+        <v>2.7</v>
       </c>
       <c r="E2" t="n">
         <v>69</v>
       </c>
       <c r="F2" t="n">
-        <v>6.45</v>
+        <v>6.19</v>
       </c>
       <c r="G2" t="n">
         <v>147</v>
       </c>
       <c r="H2" t="n">
-        <v>12.82</v>
+        <v>12.23</v>
       </c>
       <c r="I2" t="n">
-        <v>26</v>
+        <v>24.8</v>
       </c>
       <c r="J2" t="n">
         <v>87.48</v>
@@ -519,7 +519,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>nonIID(timefirst)</t>
+          <t>nonIID(plus)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -528,64 +528,64 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="D3" t="n">
-        <v>10.28</v>
+        <v>7.15</v>
       </c>
       <c r="E3" t="n">
-        <v>124</v>
+        <v>94</v>
       </c>
       <c r="F3" t="n">
-        <v>22.51</v>
+        <v>17.49</v>
       </c>
       <c r="G3" t="n">
-        <v>248</v>
+        <v>233</v>
       </c>
       <c r="H3" t="n">
-        <v>44.91</v>
+        <v>43.85</v>
       </c>
       <c r="I3" t="n">
-        <v>54.31</v>
+        <v>56.58</v>
       </c>
       <c r="J3" t="n">
-        <v>85.75</v>
+        <v>86.40000000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>nonIID(plus)</t>
+          <t>nonIID(0.5)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PyramidFL</t>
+          <t>FedDocs</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D4" t="n">
-        <v>7.15</v>
+        <v>7.27</v>
       </c>
       <c r="E4" t="n">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F4" t="n">
-        <v>17.49</v>
+        <v>16.54</v>
       </c>
       <c r="G4" t="n">
-        <v>233</v>
+        <v>185</v>
       </c>
       <c r="H4" t="n">
-        <v>43.85</v>
+        <v>33.92</v>
       </c>
       <c r="I4" t="n">
-        <v>56.58</v>
+        <v>54.97</v>
       </c>
       <c r="J4" t="n">
-        <v>86.40000000000001</v>
+        <v>86.89</v>
       </c>
     </row>
     <row r="5">
@@ -596,32 +596,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>FedDocs</t>
+          <t>TiFL</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D5" t="n">
-        <v>7.27</v>
+        <v>5.06</v>
       </c>
       <c r="E5" t="n">
-        <v>90</v>
+        <v>114</v>
       </c>
       <c r="F5" t="n">
-        <v>16.54</v>
+        <v>15.01</v>
       </c>
       <c r="G5" t="n">
-        <v>185</v>
+        <v>216</v>
       </c>
       <c r="H5" t="n">
-        <v>33.92</v>
+        <v>29.34</v>
       </c>
       <c r="I5" t="n">
-        <v>54.97</v>
+        <v>40.32</v>
       </c>
       <c r="J5" t="n">
-        <v>86.89</v>
+        <v>86.02</v>
       </c>
     </row>
     <row r="6">
@@ -632,67 +632,31 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>FedLC</t>
+          <t>FedAvg</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="D6" t="n">
-        <v>7.8</v>
+        <v>11.29</v>
       </c>
       <c r="E6" t="n">
-        <v>106</v>
+        <v>135</v>
       </c>
       <c r="F6" t="n">
-        <v>19.33</v>
+        <v>24.54</v>
       </c>
       <c r="G6" t="n">
-        <v>225</v>
+        <v>290</v>
       </c>
       <c r="H6" t="n">
-        <v>41.17</v>
+        <v>53.24</v>
       </c>
       <c r="I6" t="n">
-        <v>54.89</v>
+        <v>55.05</v>
       </c>
       <c r="J6" t="n">
-        <v>86.52</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>nonIID(0.5)</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>FedAvg</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>62</v>
-      </c>
-      <c r="D7" t="n">
-        <v>11.29</v>
-      </c>
-      <c r="E7" t="n">
-        <v>135</v>
-      </c>
-      <c r="F7" t="n">
-        <v>24.54</v>
-      </c>
-      <c r="G7" t="n">
-        <v>290</v>
-      </c>
-      <c r="H7" t="n">
-        <v>53.24</v>
-      </c>
-      <c r="I7" t="n">
-        <v>55.05</v>
-      </c>
-      <c r="J7" t="n">
         <v>85.09</v>
       </c>
     </row>
